--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Gesammelte_Datenbanken/Yukon_Geothermal_Springs.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Gesammelte_Datenbanken/Yukon_Geothermal_Springs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\Gesammelte_Datenbanken\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B488E6F-F2BE-42E9-9E15-E4699FD97705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63BADE5-BEDD-4E66-85D0-1B7C04C396AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="206">
   <si>
     <t>X</t>
   </si>
@@ -632,6 +632,12 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>LOCATION</t>
+  </si>
+  <si>
+    <t>Yukon</t>
   </si>
 </sst>
 </file>
@@ -1018,38 +1024,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI89"/>
+  <dimension ref="A1:AJ89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" customWidth="1"/>
-    <col min="12" max="14" width="9.7109375" customWidth="1"/>
-    <col min="15" max="15" width="8.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" customWidth="1"/>
-    <col min="17" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" customWidth="1"/>
-    <col min="21" max="21" width="8.7109375" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="10.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" customWidth="1"/>
-    <col min="25" max="25" width="13.7109375" customWidth="1"/>
-    <col min="26" max="26" width="20.7109375" customWidth="1"/>
-    <col min="27" max="27" width="17.7109375" customWidth="1"/>
-    <col min="28" max="28" width="13.7109375" customWidth="1"/>
-    <col min="29" max="32" width="50.7109375" customWidth="1"/>
-    <col min="33" max="33" width="13.7109375" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" customWidth="1"/>
+    <col min="2" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="9" width="11.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="15" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
+    <col min="21" max="21" width="9.7109375" customWidth="1"/>
+    <col min="22" max="22" width="8.7109375" customWidth="1"/>
+    <col min="23" max="23" width="11.7109375" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" customWidth="1"/>
+    <col min="26" max="26" width="13.7109375" customWidth="1"/>
+    <col min="27" max="27" width="20.7109375" customWidth="1"/>
+    <col min="28" max="28" width="17.7109375" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" customWidth="1"/>
+    <col min="30" max="33" width="50.7109375" customWidth="1"/>
+    <col min="34" max="34" width="13.7109375" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1057,5199 +1063,5466 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>826060.71089999902</v>
       </c>
       <c r="B2">
         <v>1007410.9552</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>34</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>54</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>120</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>109</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>72</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>21</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>49</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>1.5</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>58</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>136</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>192</v>
       </c>
-      <c r="AG2">
+      <c r="AH2">
         <v>63.405009999999997</v>
       </c>
-      <c r="AH2">
+      <c r="AI2">
         <v>-125.95569999999999</v>
       </c>
-      <c r="AI2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>863603.56750000105</v>
       </c>
       <c r="B3">
         <v>565896.20970000001</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>35</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>52</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>70</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>134</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>6.5</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>226</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>34.4</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>16.399999999999999</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>10.1</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>180</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>592</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>94.1</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>16.7</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>136</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AG3" t="s">
         <v>193</v>
       </c>
-      <c r="AG3">
+      <c r="AH3">
         <v>59.427799999999998</v>
       </c>
-      <c r="AH3">
+      <c r="AI3">
         <v>-126.09892000000001</v>
       </c>
-      <c r="AI3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>815862.70319999906</v>
       </c>
       <c r="B4">
         <v>583973.50249999901</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>36</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>48</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>15</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>125</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>77</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>41</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>34</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>725</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>77</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>64</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>0.3</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>137</v>
       </c>
-      <c r="AD4" s="2" t="s">
+      <c r="AE4" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>193</v>
       </c>
-      <c r="AG4">
+      <c r="AH4">
         <v>59.630290000000002</v>
       </c>
-      <c r="AH4">
+      <c r="AI4">
         <v>-126.90672000000001</v>
       </c>
-      <c r="AI4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>882034.31270000001</v>
       </c>
       <c r="B5">
         <v>674476.08080000104</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>37</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>54.5</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>95</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>203</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>6.4</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>667</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>345</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>86.5</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>31.4</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>9</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>4.2</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>320</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>94.1</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>3</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>5.6</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>0.6</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>-23</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>-177.9</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>122</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
         <v>133</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>138</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>169</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AG5" t="s">
         <v>194</v>
       </c>
-      <c r="AG5">
+      <c r="AH5">
         <v>60.381419999999999</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>-125.56873</v>
       </c>
-      <c r="AI5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>878957.37769999902</v>
       </c>
       <c r="B6">
         <v>662320.60990000004</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>38</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>15</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>58</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>178</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>7.3</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>423</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>225</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>53.9</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>22</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>2.1</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>1</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>250</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>24</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>3</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>1</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>0.3</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>-22.9</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>-175</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>123</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AD6" t="s">
         <v>138</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>169</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AG6" t="s">
         <v>194</v>
       </c>
-      <c r="AG6">
+      <c r="AH6">
         <v>60.275820000000003</v>
       </c>
-      <c r="AH6">
+      <c r="AI6">
         <v>-125.64785999999999</v>
       </c>
-      <c r="AI6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>876614.64469999995</v>
       </c>
       <c r="B7">
         <v>632326.04480000003</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>25.3</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>5</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>54</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>181.5</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>6.9</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>488</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>256</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>67.900000000000006</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>21</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>1.7</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>270</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>39.5</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>3</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>4.5999999999999996</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>1.3</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>-21.5</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>-172.6</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>124</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>133</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>138</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>169</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AG7" t="s">
         <v>194</v>
       </c>
-      <c r="AG7">
+      <c r="AH7">
         <v>60.009990000000002</v>
       </c>
-      <c r="AH7">
+      <c r="AI7">
         <v>-125.74744</v>
       </c>
-      <c r="AI7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>872030.9608</v>
       </c>
       <c r="B8">
         <v>653034.932399999</v>
       </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
         <v>40</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>29.2</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>65</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>232</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>6.9</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>367</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>254</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>56.8</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>27.2</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.8</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>1.3</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>270</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>30.9</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>3</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>0.4</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>0.6</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>-22.7</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>-174.4</v>
       </c>
-      <c r="X8" t="s">
+      <c r="Y8" t="s">
         <v>122</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AD8" t="s">
         <v>138</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AE8" t="s">
         <v>169</v>
       </c>
-      <c r="AF8" t="s">
+      <c r="AG8" t="s">
         <v>194</v>
       </c>
-      <c r="AG8">
+      <c r="AH8">
         <v>60.199480000000001</v>
       </c>
-      <c r="AH8">
+      <c r="AI8">
         <v>-125.78986</v>
       </c>
-      <c r="AI8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>815902.16460000002</v>
       </c>
       <c r="B9">
         <v>784649.04979999899</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>41</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>29</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>50</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>98</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>125</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>25.5</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1.4</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>2.5</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>45</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>136</v>
       </c>
-      <c r="AD9" s="2" t="s">
+      <c r="AE9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AG9" t="s">
         <v>192</v>
       </c>
-      <c r="AG9">
+      <c r="AH9">
         <v>61.42595</v>
       </c>
-      <c r="AH9">
+      <c r="AI9">
         <v>-126.57483999999999</v>
       </c>
-      <c r="AI9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>778950.87620000006</v>
       </c>
       <c r="B10">
         <v>839043.09679999901</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>42</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>21</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>2</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>92</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>200</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>39.799999999999997</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>3.9</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>4.8</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>40</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AD10" t="s">
         <v>136</v>
       </c>
-      <c r="AD10" s="2" t="s">
+      <c r="AE10" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF10" t="s">
+      <c r="AG10" t="s">
         <v>192</v>
       </c>
-      <c r="AG10">
+      <c r="AH10">
         <v>61.941499999999998</v>
       </c>
-      <c r="AH10">
+      <c r="AI10">
         <v>-127.17908</v>
       </c>
-      <c r="AI10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>775727.64599999995</v>
       </c>
       <c r="B11">
         <v>811764.51179999998</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>43</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>47</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>30</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>127</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>1.2</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>28</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.7</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>83</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AD11" t="s">
         <v>136</v>
       </c>
-      <c r="AD11" s="2" t="s">
+      <c r="AE11" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF11" t="s">
+      <c r="AG11" t="s">
         <v>194</v>
       </c>
-      <c r="AG11">
+      <c r="AH11">
         <v>61.7</v>
       </c>
-      <c r="AH11">
+      <c r="AI11">
         <v>-127.283</v>
       </c>
-      <c r="AI11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>724600.21890000103</v>
       </c>
       <c r="B12">
         <v>879786.20290000003</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>40</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AD12" t="s">
         <v>139</v>
       </c>
-      <c r="AD12" s="2" t="s">
+      <c r="AE12" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AG12" t="s">
         <v>192</v>
       </c>
-      <c r="AG12">
+      <c r="AH12">
         <v>62.343000000000004</v>
       </c>
-      <c r="AH12">
+      <c r="AI12">
         <v>-128.1591</v>
       </c>
-      <c r="AI12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>686719.00929999899</v>
       </c>
       <c r="B13">
         <v>930361.79749999905</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>45</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>64</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>60</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>142</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>2.8</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>56</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>1.7</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>109</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AD13" t="s">
         <v>136</v>
       </c>
-      <c r="AD13" s="2" t="s">
+      <c r="AE13" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF13" t="s">
+      <c r="AG13" t="s">
         <v>194</v>
       </c>
-      <c r="AG13">
+      <c r="AH13">
         <v>62.817</v>
       </c>
-      <c r="AH13">
+      <c r="AI13">
         <v>-128.833</v>
       </c>
-      <c r="AI13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>670696.54109999898</v>
       </c>
       <c r="B14">
         <v>1062913.3208000001</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>46</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>8.5</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>25</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>85</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>7.88</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>270</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>58.8</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>200</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>3.64</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>77.5</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>555</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>0.03</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>34</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>263</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AD14" t="s">
         <v>140</v>
       </c>
-      <c r="AD14" s="2" t="s">
+      <c r="AE14" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AG14" t="s">
         <v>194</v>
       </c>
-      <c r="AG14">
+      <c r="AH14">
         <v>64.010999999999996</v>
       </c>
-      <c r="AH14">
+      <c r="AI14">
         <v>-129.00361000000001</v>
       </c>
-      <c r="AI14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>952004.55980000098</v>
       </c>
       <c r="B15">
         <v>780679.69559999905</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>47</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>37</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>23</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>108</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>271</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>660</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>56</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>2277</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>1</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>134</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AD15" t="s">
         <v>141</v>
       </c>
-      <c r="AD15" s="2" t="s">
+      <c r="AE15" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="AF15" t="s">
+      <c r="AG15" t="s">
         <v>192</v>
       </c>
-      <c r="AG15">
+      <c r="AH15">
         <v>61.252380000000002</v>
       </c>
-      <c r="AH15">
+      <c r="AI15">
         <v>-124.05754</v>
       </c>
-      <c r="AI15">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>697500.90040000004</v>
       </c>
       <c r="B16">
         <v>881243.319599999</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>48</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>58</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>40</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>124</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>1.9</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>67</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>1.4</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>78</v>
       </c>
-      <c r="AC16" t="s">
+      <c r="AD16" t="s">
         <v>136</v>
       </c>
-      <c r="AD16" s="2" t="s">
+      <c r="AE16" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF16" t="s">
+      <c r="AG16" t="s">
         <v>192</v>
       </c>
-      <c r="AG16">
+      <c r="AH16">
         <v>62.371670000000002</v>
       </c>
-      <c r="AH16">
+      <c r="AI16">
         <v>-128.67981</v>
       </c>
-      <c r="AI16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>722243.62120000098</v>
       </c>
       <c r="B17">
         <v>933138.52619999996</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>49</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>45</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>35</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>108</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>140</v>
-      </c>
-      <c r="M17">
-        <v>50.2</v>
       </c>
       <c r="N17">
         <v>50.2</v>
       </c>
       <c r="O17">
+        <v>50.2</v>
+      </c>
+      <c r="P17">
         <v>33.799999999999997</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>56</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AD17" t="s">
         <v>139</v>
       </c>
-      <c r="AD17" s="2" t="s">
+      <c r="AE17" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="AF17" t="s">
+      <c r="AG17" t="s">
         <v>192</v>
       </c>
-      <c r="AG17">
+      <c r="AH17">
         <v>62.821680000000001</v>
       </c>
-      <c r="AH17">
+      <c r="AI17">
         <v>-128.1336</v>
       </c>
-      <c r="AI17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>734428.89020000002</v>
       </c>
       <c r="B18">
         <v>916344.91879999998</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>50</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>44</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>30</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>106</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>105</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>25.5</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>22</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>23.8</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>54</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AD18" t="s">
         <v>139</v>
       </c>
-      <c r="AD18" s="2" t="s">
+      <c r="AE18" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="AF18" t="s">
+      <c r="AG18" t="s">
         <v>192</v>
       </c>
-      <c r="AG18">
+      <c r="AH18">
         <v>62.663800000000002</v>
       </c>
-      <c r="AH18">
+      <c r="AI18">
         <v>-127.91880999999999</v>
       </c>
-      <c r="AI18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>648925.03949999996</v>
       </c>
       <c r="B19">
         <v>821724.23169999896</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>51</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>16</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>20</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>85</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>7.3</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>47</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>10.1</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>3.3</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.5</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>109</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>12.2</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>34</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>0.2</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AD19" t="s">
         <v>142</v>
       </c>
-      <c r="AD19" s="2" t="s">
+      <c r="AE19" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AE19" t="s">
+      <c r="AF19" t="s">
         <v>185</v>
       </c>
-      <c r="AF19" t="s">
+      <c r="AG19" t="s">
         <v>192</v>
       </c>
-      <c r="AG19">
+      <c r="AH19">
         <v>61.861370000000001</v>
       </c>
-      <c r="AH19">
+      <c r="AI19">
         <v>-129.66928999999999</v>
       </c>
-      <c r="AI19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>613781.95659999899</v>
       </c>
       <c r="B20">
         <v>979010.19869999995</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>52</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>33</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>1</v>
       </c>
-      <c r="AC20" t="s">
+      <c r="AD20" t="s">
         <v>143</v>
       </c>
-      <c r="AD20" t="s">
+      <c r="AE20" t="s">
         <v>169</v>
       </c>
-      <c r="AF20" t="s">
+      <c r="AG20" t="s">
         <v>192</v>
       </c>
-      <c r="AG20">
+      <c r="AH20">
         <v>63.283180000000002</v>
       </c>
-      <c r="AH20">
+      <c r="AI20">
         <v>-130.22963999999999</v>
       </c>
-      <c r="AI20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>725098.75190000003</v>
       </c>
       <c r="B21">
         <v>836451.0196</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>53</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>41</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>30</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>109</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>7.6</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>1.2</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>47</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>1.2</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>58</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AD21" t="s">
         <v>136</v>
       </c>
-      <c r="AD21" s="2" t="s">
+      <c r="AE21" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF21" t="s">
+      <c r="AG21" t="s">
         <v>192</v>
       </c>
-      <c r="AG21">
+      <c r="AH21">
         <v>61.954909999999998</v>
       </c>
-      <c r="AH21">
+      <c r="AI21">
         <v>-128.20613</v>
       </c>
-      <c r="AI21">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>344595.82709999901</v>
       </c>
       <c r="B22">
         <v>712453.20200000005</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>54</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>47</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>6.6</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>96</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>6.6</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>2905</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>611</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>79.2</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>35.1</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>8.8000000000000007</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>112</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>1670</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>89.1</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>1</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>3.2</v>
       </c>
-      <c r="AC22" t="s">
+      <c r="AD22" t="s">
         <v>136</v>
       </c>
-      <c r="AD22" s="2" t="s">
+      <c r="AE22" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF22" t="s">
+      <c r="AG22" t="s">
         <v>193</v>
       </c>
-      <c r="AG22">
+      <c r="AH22">
         <v>60.878900000000002</v>
       </c>
-      <c r="AH22">
+      <c r="AI22">
         <v>-135.36010999999999</v>
       </c>
-      <c r="AI22">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>355686.84649999999</v>
       </c>
       <c r="B23">
         <v>698883.67159999895</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="s">
+        <v>205</v>
+      </c>
+      <c r="D23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>55</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>12.7</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>1</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>87</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>164</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>7.6</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>336</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>182</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>49.5</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>14.3</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>5.8</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>1.4</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>198</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>28</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>3</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>1</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>0.4</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>-20.6</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <v>-167.1</v>
       </c>
-      <c r="X23" t="s">
+      <c r="Y23" t="s">
         <v>125</v>
       </c>
-      <c r="AC23" t="s">
+      <c r="AD23" t="s">
         <v>144</v>
       </c>
-      <c r="AD23" t="s">
+      <c r="AE23" t="s">
         <v>169</v>
       </c>
-      <c r="AF23" t="s">
+      <c r="AG23" t="s">
         <v>194</v>
       </c>
-      <c r="AG23">
+      <c r="AH23">
         <v>60.76146</v>
       </c>
-      <c r="AH23">
+      <c r="AI23">
         <v>-135.14581999999999</v>
       </c>
-      <c r="AI23">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>356616.84019999998</v>
       </c>
       <c r="B24">
         <v>697844.38130000001</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>56</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>18.5</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>1</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>54</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>160</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>7.6</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>347</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>190</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>51</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>15.1</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>6.9</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>1.7</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>208</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>30.1</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>3</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>1</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>0.5</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>-21.3</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>-169.8</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Y24" t="s">
         <v>126</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AA24" t="s">
         <v>133</v>
       </c>
-      <c r="AC24" t="s">
+      <c r="AD24" t="s">
         <v>145</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AE24" t="s">
         <v>169</v>
       </c>
-      <c r="AF24" t="s">
+      <c r="AG24" t="s">
         <v>194</v>
       </c>
-      <c r="AG24">
+      <c r="AH24">
         <v>60.752479999999998</v>
       </c>
-      <c r="AH24">
+      <c r="AI24">
         <v>-135.12799999999999</v>
       </c>
-      <c r="AI24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>352712.62580000103</v>
       </c>
       <c r="B25">
         <v>702080.192600001</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>57</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>15.8</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>7.8</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>360</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>213</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>60.1</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>15.3</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>7.3</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>2.1</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>219</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>43.9</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>3</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>1.2</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>0.4</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>-20.8</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>-166.8</v>
       </c>
-      <c r="X25" t="s">
+      <c r="Y25" t="s">
         <v>127</v>
       </c>
-      <c r="AC25" t="s">
+      <c r="AD25" t="s">
         <v>144</v>
       </c>
-      <c r="AD25" t="s">
+      <c r="AE25" t="s">
         <v>169</v>
       </c>
-      <c r="AF25" t="s">
+      <c r="AG25" t="s">
         <v>194</v>
       </c>
-      <c r="AG25">
+      <c r="AH25">
         <v>60.789020000000001</v>
       </c>
-      <c r="AH25">
+      <c r="AI25">
         <v>-135.20277999999999</v>
       </c>
-      <c r="AI25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>352798.39030000003</v>
       </c>
       <c r="B26">
         <v>702044.21979999903</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="s">
+        <v>205</v>
+      </c>
+      <c r="D26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>58</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>12</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>1</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>39</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>163</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>7.7</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>404</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>162</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>44.8</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>12</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>5.5</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>1.4</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>179</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>27</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>3</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>0.8</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>0.3</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>-19.5</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <v>-161.6</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Y26" t="s">
         <v>128</v>
       </c>
-      <c r="AC26" t="s">
+      <c r="AD26" t="s">
         <v>144</v>
       </c>
-      <c r="AD26" t="s">
+      <c r="AE26" t="s">
         <v>169</v>
       </c>
-      <c r="AF26" t="s">
+      <c r="AG26" t="s">
         <v>194</v>
       </c>
-      <c r="AG26">
+      <c r="AH26">
         <v>60.788730000000001</v>
       </c>
-      <c r="AH26">
+      <c r="AI26">
         <v>-135.20117999999999</v>
       </c>
-      <c r="AI26">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>357671.04519999999</v>
       </c>
       <c r="B27">
         <v>697114.46660000097</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>59</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>33</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>36</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>7.7</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>2.9</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>1.2</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>136</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>9.4</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>8.8000000000000007</v>
-      </c>
-      <c r="T27">
-        <v>0.2</v>
       </c>
       <c r="U27">
         <v>0.2</v>
       </c>
       <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
         <v>-19.5</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>-158.80000000000001</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>135</v>
       </c>
-      <c r="AC27" t="s">
+      <c r="AD27" t="s">
         <v>146</v>
       </c>
-      <c r="AD27" s="2" t="s">
+      <c r="AE27" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="AF27" t="s">
+      <c r="AG27" t="s">
         <v>194</v>
       </c>
-      <c r="AG27">
+      <c r="AH27">
         <v>60.746319999999997</v>
       </c>
-      <c r="AH27">
+      <c r="AI27">
         <v>-135.10814999999999</v>
       </c>
-      <c r="AI27">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>337863.47729999898</v>
       </c>
       <c r="B28">
         <v>957026.848999999</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="s">
+        <v>205</v>
+      </c>
+      <c r="D28">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>60</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>54.5</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>30</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>157</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>120.7</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>7.2</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>268</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>4</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>1.4</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>0</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>40.9</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>43</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>14.9</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>21.3</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>0.9</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>7.6</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <v>-21.9</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <v>-169.3</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AD28" t="s">
         <v>147</v>
       </c>
-      <c r="AD28" t="s">
+      <c r="AE28" t="s">
         <v>169</v>
       </c>
-      <c r="AF28" t="s">
+      <c r="AG28" t="s">
         <v>194</v>
       </c>
-      <c r="AG28">
+      <c r="AH28">
         <v>63.067610000000002</v>
       </c>
-      <c r="AH28">
+      <c r="AI28">
         <v>-135.71164999999999</v>
       </c>
-      <c r="AI28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>262654.00770000002</v>
       </c>
       <c r="B29">
         <v>1033086.8814</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="s">
+        <v>205</v>
+      </c>
+      <c r="D29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>61</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>25.1</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>116</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>122</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>8.8000000000000007</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>441</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>17</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>6.2</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>0.2</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>75.900000000000006</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>100</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>63.2</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>3</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>11.2</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>9.4</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>-21.5</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <v>-172.2</v>
       </c>
-      <c r="X29" t="s">
+      <c r="Y29" t="s">
         <v>129</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AD29" t="s">
         <v>148</v>
       </c>
-      <c r="AD29" t="s">
+      <c r="AE29" t="s">
         <v>169</v>
       </c>
-      <c r="AF29" t="s">
+      <c r="AG29" t="s">
         <v>194</v>
       </c>
-      <c r="AG29">
+      <c r="AH29">
         <v>63.705260000000003</v>
       </c>
-      <c r="AH29">
+      <c r="AI29">
         <v>-137.31082000000001</v>
       </c>
-      <c r="AI29">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>203287.19289999999</v>
       </c>
       <c r="B30">
         <v>724263.87670000095</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>62</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>17.7</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>5</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>111</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>100.1</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>8.1</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>660</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>79</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>10.5</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>9.6</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>111</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>1.9</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>332</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>32.700000000000003</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>12.4</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <v>26.6</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>0.3</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>-25.6</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <v>-198</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Y30" t="s">
         <v>122</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="Z30" t="s">
         <v>132</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AA30" t="s">
         <v>133</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AD30" t="s">
         <v>149</v>
       </c>
-      <c r="AD30" t="s">
+      <c r="AE30" t="s">
         <v>169</v>
       </c>
-      <c r="AF30" t="s">
+      <c r="AG30" t="s">
         <v>193</v>
       </c>
-      <c r="AG30">
+      <c r="AH30">
         <v>60.901440000000001</v>
       </c>
-      <c r="AH30">
+      <c r="AI30">
         <v>-137.96969000000001</v>
       </c>
-      <c r="AI30">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ30">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>394186.81819999998</v>
       </c>
       <c r="B31">
         <v>1120341.1089000001</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>63</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>45.6</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>3</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>80</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>49.7</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>7.3</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>390</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>170</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>42.7</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>15.5</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>22.1</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>5.6</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>169</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>27</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>3</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <v>42.6</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>0.5</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <v>-21.8</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <v>-173.6</v>
       </c>
-      <c r="X31" t="s">
+      <c r="Y31" t="s">
         <v>130</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AA31" t="s">
         <v>133</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AD31" t="s">
         <v>150</v>
       </c>
-      <c r="AD31" t="s">
+      <c r="AE31" t="s">
         <v>169</v>
       </c>
-      <c r="AE31" t="s">
+      <c r="AF31" t="s">
         <v>186</v>
       </c>
-      <c r="AF31" t="s">
+      <c r="AG31" t="s">
         <v>194</v>
       </c>
-      <c r="AG31">
+      <c r="AH31">
         <v>64.55104</v>
       </c>
-      <c r="AH31">
+      <c r="AI31">
         <v>-134.70977999999999</v>
       </c>
-      <c r="AI31">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>380139.98670000001</v>
       </c>
       <c r="B32">
         <v>1127375.6861</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="s">
+        <v>205</v>
+      </c>
+      <c r="D32">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>64</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>10.199999999999999</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>28</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>8.1999999999999993</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>207</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>106</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>22.5</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>12.1</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>0.7</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>0.2</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>125</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>8.1999999999999993</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>3</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <v>7.7</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <v>0.6</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>0.1</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <v>-22.7</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <v>-172.7</v>
       </c>
-      <c r="AC32" t="s">
+      <c r="AD32" t="s">
         <v>151</v>
       </c>
-      <c r="AD32" t="s">
+      <c r="AE32" t="s">
         <v>169</v>
       </c>
-      <c r="AF32" t="s">
+      <c r="AG32" t="s">
         <v>194</v>
       </c>
-      <c r="AG32">
+      <c r="AH32">
         <v>64.609319999999997</v>
       </c>
-      <c r="AH32">
+      <c r="AI32">
         <v>-135.00864999999999</v>
       </c>
-      <c r="AI32">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>887336.29109999898</v>
       </c>
       <c r="B33">
         <v>654610.74929999898</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="s">
+        <v>205</v>
+      </c>
+      <c r="D33">
         <v>32</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>65</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>53</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>40</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>92</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>220</v>
       </c>
-      <c r="I33">
-        <v>7</v>
-      </c>
       <c r="J33">
+        <v>7</v>
+      </c>
+      <c r="K33">
         <v>554</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>284</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>81</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>19.8</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>5.6</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>4.2</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>230</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>96.2</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>3</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <v>5.2</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <v>0.6</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <v>-23</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <v>-176</v>
       </c>
-      <c r="X33" t="s">
+      <c r="Y33" t="s">
         <v>122</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AA33" t="s">
         <v>133</v>
       </c>
-      <c r="AC33" t="s">
+      <c r="AD33" t="s">
         <v>138</v>
       </c>
-      <c r="AD33" t="s">
+      <c r="AE33" t="s">
         <v>169</v>
       </c>
-      <c r="AF33" t="s">
+      <c r="AG33" t="s">
         <v>194</v>
       </c>
-      <c r="AG33">
+      <c r="AH33">
         <v>60.198729999999998</v>
       </c>
-      <c r="AH33">
+      <c r="AI33">
         <v>-125.51287000000001</v>
       </c>
-      <c r="AI33">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>886736.119000001</v>
       </c>
       <c r="B34">
         <v>654494.02390000003</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="s">
+        <v>205</v>
+      </c>
+      <c r="D34">
         <v>33</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>66</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>43</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>30</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>94</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>217.5</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>6.8</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>538</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>282</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>82.9</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>18.3</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>5.6</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>230</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>98.3</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>3</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>5.0999999999999996</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>0.6</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>-22.8</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <v>-175.2</v>
       </c>
-      <c r="X34" t="s">
+      <c r="Y34" t="s">
         <v>122</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AA34" t="s">
         <v>133</v>
       </c>
-      <c r="AC34" t="s">
+      <c r="AD34" t="s">
         <v>138</v>
       </c>
-      <c r="AD34" t="s">
+      <c r="AE34" t="s">
         <v>169</v>
       </c>
-      <c r="AF34" t="s">
+      <c r="AG34" t="s">
         <v>194</v>
       </c>
-      <c r="AG34">
+      <c r="AH34">
         <v>60.198279999999997</v>
       </c>
-      <c r="AH34">
+      <c r="AI34">
         <v>-125.52384000000001</v>
       </c>
-      <c r="AI34">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>781419.96620000002</v>
       </c>
       <c r="B35">
         <v>639331.67610000097</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="s">
+        <v>205</v>
+      </c>
+      <c r="D35">
         <v>34</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>67</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>13.2</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>45</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>169.5</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>6.6</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>531</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>285</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>86.3</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>17</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>1.3</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>0.7</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>340</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>19</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>3</v>
       </c>
-      <c r="T35">
+      <c r="U35">
         <v>0.3</v>
       </c>
-      <c r="U35">
+      <c r="V35">
         <v>0.2</v>
       </c>
-      <c r="V35">
+      <c r="W35">
         <v>-22.6</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <v>-172.2</v>
       </c>
-      <c r="X35" t="s">
+      <c r="Y35" t="s">
         <v>131</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="AA35" t="s">
         <v>133</v>
       </c>
-      <c r="AC35" t="s">
+      <c r="AD35" t="s">
         <v>138</v>
       </c>
-      <c r="AD35" t="s">
+      <c r="AE35" t="s">
         <v>169</v>
       </c>
-      <c r="AF35" t="s">
+      <c r="AG35" t="s">
         <v>194</v>
       </c>
-      <c r="AG35">
+      <c r="AH35">
         <v>60.152349999999998</v>
       </c>
-      <c r="AH35">
+      <c r="AI35">
         <v>-127.43579</v>
       </c>
-      <c r="AI35">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>760175.30390000006</v>
       </c>
       <c r="B36">
         <v>806792.72430000105</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="s">
+        <v>205</v>
+      </c>
+      <c r="D36">
         <v>35</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>68</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>11</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>1.5</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>96</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>7.06</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>470</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>49</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>24</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>5.98</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>897</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>36</v>
       </c>
-      <c r="R36">
+      <c r="S36">
         <v>0.03</v>
       </c>
-      <c r="S36">
+      <c r="T36">
         <v>43</v>
       </c>
-      <c r="T36">
+      <c r="U36">
         <v>1.7</v>
       </c>
-      <c r="AC36" t="s">
+      <c r="AD36" t="s">
         <v>140</v>
       </c>
-      <c r="AD36" s="2" t="s">
+      <c r="AE36" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF36" t="s">
+      <c r="AG36" t="s">
         <v>194</v>
       </c>
-      <c r="AG36">
+      <c r="AH36">
         <v>61.666670000000003</v>
       </c>
-      <c r="AH36">
+      <c r="AI36">
         <v>-127.58333</v>
       </c>
-      <c r="AI36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>595593.68530000001</v>
       </c>
       <c r="B37">
         <v>324213.06210000103</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="s">
+        <v>205</v>
+      </c>
+      <c r="D37">
         <v>36</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>69</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>42.5</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>3.2</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>120</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>6.2</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>2400</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>138</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>20.399999999999999</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>190</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>18</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>441</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>150</v>
       </c>
-      <c r="S37">
+      <c r="T37">
         <v>71.5</v>
       </c>
-      <c r="T37">
+      <c r="U37">
         <v>209</v>
       </c>
-      <c r="U37">
+      <c r="V37">
         <v>1.7</v>
       </c>
-      <c r="AC37" t="s">
+      <c r="AD37" t="s">
         <v>136</v>
       </c>
-      <c r="AD37" s="2" t="s">
+      <c r="AE37" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF37" t="s">
+      <c r="AG37" t="s">
         <v>194</v>
       </c>
-      <c r="AG37">
+      <c r="AH37">
         <v>57.404350000000001</v>
       </c>
-      <c r="AH37">
+      <c r="AI37">
         <v>-130.91825</v>
       </c>
-      <c r="AI37">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>572811.91139999998</v>
       </c>
       <c r="B38">
         <v>280795.99109999998</v>
       </c>
-      <c r="C38">
+      <c r="C38" t="s">
+        <v>205</v>
+      </c>
+      <c r="D38">
         <v>37</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>70</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>48.5</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>0.2</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>118</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>6.59</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>64.8</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>12.3</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>396</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>16.3</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>963</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>145</v>
       </c>
-      <c r="S38">
+      <c r="T38">
         <v>69.900000000000006</v>
       </c>
-      <c r="T38">
+      <c r="U38">
         <v>63.4</v>
       </c>
-      <c r="U38">
+      <c r="V38">
         <v>3.89</v>
       </c>
-      <c r="AC38" t="s">
+      <c r="AD38" t="s">
         <v>136</v>
       </c>
-      <c r="AD38" s="2" t="s">
+      <c r="AE38" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF38" t="s">
+      <c r="AG38" t="s">
         <v>194</v>
       </c>
-      <c r="AG38">
+      <c r="AH38">
         <v>57.01681</v>
       </c>
-      <c r="AH38">
+      <c r="AI38">
         <v>-131.30860999999999</v>
       </c>
-      <c r="AI38">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>607236.62159999995</v>
       </c>
       <c r="B39">
         <v>358937.80249999999</v>
       </c>
-      <c r="C39">
+      <c r="C39" t="s">
+        <v>205</v>
+      </c>
+      <c r="D39">
         <v>38</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>71</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>46</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>2</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>177</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>6.72</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>3000</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>167</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>141</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>515</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>54.6</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>2440</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <v>5.01</v>
       </c>
-      <c r="S39">
+      <c r="T39">
         <v>191</v>
       </c>
-      <c r="T39">
+      <c r="U39">
         <v>52.7</v>
       </c>
-      <c r="U39">
+      <c r="V39">
         <v>2.3E-2</v>
       </c>
-      <c r="AC39" t="s">
+      <c r="AD39" t="s">
         <v>136</v>
       </c>
-      <c r="AD39" s="2" t="s">
+      <c r="AE39" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF39" t="s">
+      <c r="AG39" t="s">
         <v>194</v>
       </c>
-      <c r="AG39">
+      <c r="AH39">
         <v>57.714869999999998</v>
       </c>
-      <c r="AH39">
+      <c r="AI39">
         <v>-130.70947000000001</v>
       </c>
-      <c r="AI39">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>604896.18420000002</v>
       </c>
       <c r="B40">
         <v>365213.06430000102</v>
       </c>
-      <c r="C40">
+      <c r="C40" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40">
         <v>39</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>72</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>36</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>3.5</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>154</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>6.01</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>2780</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>126</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>104</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>659</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>49</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>2512</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>0.62</v>
       </c>
-      <c r="S40">
+      <c r="T40">
         <v>134</v>
       </c>
-      <c r="T40">
+      <c r="U40">
         <v>51</v>
       </c>
-      <c r="U40">
+      <c r="V40">
         <v>0.25</v>
       </c>
-      <c r="AC40" t="s">
+      <c r="AD40" t="s">
         <v>136</v>
       </c>
-      <c r="AD40" s="2" t="s">
+      <c r="AE40" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF40" t="s">
+      <c r="AG40" t="s">
         <v>194</v>
       </c>
-      <c r="AG40">
+      <c r="AH40">
         <v>57.772060000000003</v>
       </c>
-      <c r="AH40">
+      <c r="AI40">
         <v>-130.74563000000001</v>
       </c>
-      <c r="AI40">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>354071.28339999903</v>
       </c>
       <c r="B41">
         <v>716161.38110000105</v>
       </c>
-      <c r="C41">
+      <c r="C41" t="s">
+        <v>205</v>
+      </c>
+      <c r="D41">
         <v>40</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>73</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>13.7</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>4</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>110</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>108</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>10.07</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>624</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>14</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>5.8</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>0</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>126</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>2.2999999999999998</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>12</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>185</v>
       </c>
-      <c r="R41">
+      <c r="S41">
         <v>20</v>
       </c>
-      <c r="S41">
+      <c r="T41">
         <v>58.4</v>
       </c>
-      <c r="T41">
+      <c r="U41">
         <v>34.799999999999997</v>
       </c>
-      <c r="U41">
+      <c r="V41">
         <v>9.85</v>
       </c>
-      <c r="V41">
+      <c r="W41">
         <v>-22.42</v>
       </c>
-      <c r="W41">
+      <c r="X41">
         <v>-177.25</v>
       </c>
-      <c r="X41" t="s">
+      <c r="Y41" t="s">
         <v>129</v>
       </c>
-      <c r="AC41" t="s">
+      <c r="AD41" t="s">
         <v>152</v>
       </c>
-      <c r="AD41" t="s">
+      <c r="AE41" t="s">
         <v>169</v>
       </c>
-      <c r="AE41" t="s">
+      <c r="AF41" t="s">
         <v>187</v>
       </c>
-      <c r="AF41" t="s">
+      <c r="AG41" t="s">
         <v>194</v>
       </c>
-      <c r="AG41">
+      <c r="AH41">
         <v>60.915894000000002</v>
       </c>
-      <c r="AH41">
+      <c r="AI41">
         <v>-135.18883</v>
       </c>
-      <c r="AI41">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>404006.80489999999</v>
       </c>
       <c r="B42">
         <v>610586.05629999901</v>
       </c>
-      <c r="C42">
+      <c r="C42" t="s">
+        <v>205</v>
+      </c>
+      <c r="D42">
         <v>41</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>74</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>9.5</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>25</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>83</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>7.53</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>61</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>13</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>1.65</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>0.8</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>134</v>
       </c>
-      <c r="Q42">
+      <c r="R42">
         <v>5.4</v>
       </c>
-      <c r="S42">
+      <c r="T42">
         <v>32</v>
       </c>
-      <c r="T42">
+      <c r="U42">
         <v>0.2</v>
       </c>
-      <c r="AC42" t="s">
+      <c r="AD42" t="s">
         <v>142</v>
       </c>
-      <c r="AD42" s="2" t="s">
+      <c r="AE42" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF42" t="s">
+      <c r="AG42" t="s">
         <v>194</v>
       </c>
-      <c r="AG42">
+      <c r="AH42">
         <v>59.983330000000002</v>
       </c>
-      <c r="AH42">
+      <c r="AI42">
         <v>-134.21666999999999</v>
       </c>
-      <c r="AI42">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>403429.4792</v>
       </c>
       <c r="B43">
         <v>609026.33219999995</v>
       </c>
-      <c r="C43">
+      <c r="C43" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43">
         <v>42</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>75</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>15</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>20</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>91</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>7.29</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>68</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>15.8</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>2.85</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>1.04</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>122</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>7.5</v>
       </c>
-      <c r="S43">
+      <c r="T43">
         <v>39</v>
       </c>
-      <c r="T43">
+      <c r="U43">
         <v>0.1</v>
       </c>
-      <c r="AC43" t="s">
+      <c r="AD43" t="s">
         <v>142</v>
       </c>
-      <c r="AD43" s="2" t="s">
+      <c r="AE43" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF43" t="s">
+      <c r="AG43" t="s">
         <v>194</v>
       </c>
-      <c r="AG43">
+      <c r="AH43">
         <v>59.969169999999998</v>
       </c>
-      <c r="AH43">
+      <c r="AI43">
         <v>-134.22622999999999</v>
       </c>
-      <c r="AI43">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>552605.09550000005</v>
       </c>
       <c r="B44">
         <v>165578.79250000001</v>
       </c>
-      <c r="C44">
+      <c r="C44" t="s">
+        <v>205</v>
+      </c>
+      <c r="D44">
         <v>43</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>76</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>88.3</v>
       </c>
-      <c r="AC44" t="s">
+      <c r="AD44" t="s">
         <v>153</v>
       </c>
-      <c r="AD44" s="2" t="s">
+      <c r="AE44" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AF44" t="s">
+      <c r="AG44" t="s">
         <v>195</v>
       </c>
-      <c r="AG44">
+      <c r="AH44">
         <v>55.977824499999997</v>
       </c>
-      <c r="AH44">
+      <c r="AI44">
         <v>-131.6640596</v>
       </c>
-      <c r="AI44">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>558705.88910000003</v>
       </c>
       <c r="B45">
         <v>160374.28559999901</v>
       </c>
-      <c r="C45">
+      <c r="C45" t="s">
+        <v>205</v>
+      </c>
+      <c r="D45">
         <v>44</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>77</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>74</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>1.7</v>
       </c>
-      <c r="AC45" t="s">
+      <c r="AD45" t="s">
         <v>153</v>
       </c>
-      <c r="AD45" s="2" t="s">
+      <c r="AE45" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AF45" t="s">
+      <c r="AG45" t="s">
         <v>195</v>
       </c>
-      <c r="AG45">
+      <c r="AH45">
         <v>55.929937899999999</v>
       </c>
-      <c r="AH45">
+      <c r="AI45">
         <v>-131.56833900000001</v>
       </c>
-      <c r="AI45">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>590862.40819999902</v>
       </c>
       <c r="B46">
         <v>153851.222100001</v>
       </c>
-      <c r="C46">
+      <c r="C46" t="s">
+        <v>205</v>
+      </c>
+      <c r="D46">
         <v>45</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>78</v>
       </c>
-      <c r="AC46" t="s">
+      <c r="AD46" t="s">
         <v>154</v>
       </c>
-      <c r="AD46" s="2" t="s">
+      <c r="AE46" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AF46" t="s">
+      <c r="AG46" t="s">
         <v>195</v>
       </c>
-      <c r="AG46">
+      <c r="AH46">
         <v>55.865437</v>
       </c>
-      <c r="AH46">
+      <c r="AI46">
         <v>-131.06049999999999</v>
       </c>
-      <c r="AI46">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>565171.02119999903</v>
       </c>
       <c r="B47">
         <v>193591.95199999999</v>
       </c>
-      <c r="C47">
+      <c r="C47" t="s">
+        <v>205</v>
+      </c>
+      <c r="D47">
         <v>46</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>79</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>57</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0.4</v>
       </c>
-      <c r="AC47" t="s">
+      <c r="AD47" t="s">
         <v>155</v>
       </c>
-      <c r="AD47" s="2" t="s">
+      <c r="AE47" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AF47" t="s">
+      <c r="AG47" t="s">
         <v>195</v>
       </c>
-      <c r="AG47">
+      <c r="AH47">
         <v>56.2296634</v>
       </c>
-      <c r="AH47">
+      <c r="AI47">
         <v>-131.45708189999999</v>
       </c>
-      <c r="AI47">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ47">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>-3404995.0951999999</v>
       </c>
       <c r="B48">
         <v>3909352.9440000001</v>
       </c>
-      <c r="C48">
+      <c r="C48" t="s">
+        <v>205</v>
+      </c>
+      <c r="D48">
         <v>47</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>80</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>26</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>0.5</v>
       </c>
-      <c r="AC48" t="s">
+      <c r="AD48" t="s">
         <v>155</v>
       </c>
-      <c r="AD48" s="2" t="s">
+      <c r="AE48" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AF48" t="s">
+      <c r="AG48" t="s">
         <v>195</v>
       </c>
-      <c r="AG48">
+      <c r="AH48">
         <v>56.675502100000003</v>
       </c>
-      <c r="AH48">
+      <c r="AI48">
         <v>131.89327109999999</v>
       </c>
-      <c r="AI48">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>725248.70219999901</v>
       </c>
       <c r="B49">
         <v>836302.54029999999</v>
       </c>
-      <c r="C49">
+      <c r="C49" t="s">
+        <v>205</v>
+      </c>
+      <c r="D49">
         <v>48</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>81</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>29</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>30</v>
       </c>
-      <c r="AC49" t="s">
+      <c r="AD49" t="s">
         <v>136</v>
       </c>
-      <c r="AD49" s="2" t="s">
+      <c r="AE49" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AF49" t="s">
+      <c r="AG49" t="s">
         <v>192</v>
       </c>
-      <c r="AG49">
+      <c r="AH49">
         <v>61.953490000000002</v>
       </c>
-      <c r="AH49">
+      <c r="AI49">
         <v>-128.20347000000001</v>
       </c>
-      <c r="AI49">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>713536.347899999</v>
       </c>
       <c r="B50">
         <v>853570.88649999897</v>
       </c>
-      <c r="C50">
+      <c r="C50" t="s">
+        <v>205</v>
+      </c>
+      <c r="D50">
         <v>49</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>82</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>32</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>40</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>66</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>19</v>
       </c>
-      <c r="M50">
+      <c r="N50">
         <v>12.9</v>
       </c>
-      <c r="N50">
+      <c r="O50">
         <v>0.8</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <v>0.7</v>
       </c>
-      <c r="S50">
+      <c r="T50">
         <v>21</v>
       </c>
-      <c r="AC50" t="s">
+      <c r="AD50" t="s">
         <v>139</v>
       </c>
-      <c r="AD50" s="2" t="s">
+      <c r="AE50" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="AF50" t="s">
+      <c r="AG50" t="s">
         <v>194</v>
       </c>
-      <c r="AG50">
+      <c r="AH50">
         <v>62.115000000000002</v>
       </c>
-      <c r="AH50">
+      <c r="AI50">
         <v>-128.405</v>
       </c>
-      <c r="AI50">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>746584.92919999897</v>
       </c>
       <c r="B51">
         <v>777121.64049999998</v>
       </c>
-      <c r="C51">
+      <c r="C51" t="s">
+        <v>205</v>
+      </c>
+      <c r="D51">
         <v>50</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>83</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>3</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>40</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>82</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>7.4</v>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>110</v>
       </c>
-      <c r="M51">
+      <c r="N51">
         <v>7.5</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>12</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <v>1.4</v>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>201</v>
       </c>
-      <c r="Q51">
+      <c r="R51">
         <v>36</v>
       </c>
-      <c r="S51">
+      <c r="T51">
         <v>31</v>
       </c>
-      <c r="T51">
+      <c r="U51">
         <v>1.5</v>
       </c>
-      <c r="AC51" t="s">
+      <c r="AD51" t="s">
         <v>142</v>
       </c>
-      <c r="AD51" s="2" t="s">
+      <c r="AE51" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF51" t="s">
+      <c r="AG51" t="s">
         <v>196</v>
       </c>
-      <c r="AG51">
+      <c r="AH51">
         <v>61.410299999999999</v>
       </c>
-      <c r="AH51">
+      <c r="AI51">
         <v>-127.88</v>
       </c>
-      <c r="AI51">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ51">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>204006.26789999899</v>
       </c>
       <c r="B52">
         <v>564618.04990000103</v>
       </c>
-      <c r="C52">
+      <c r="C52" t="s">
+        <v>205</v>
+      </c>
+      <c r="D52">
         <v>51</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>84</v>
       </c>
-      <c r="AC52" t="s">
+      <c r="AD52" t="s">
         <v>156</v>
       </c>
-      <c r="AD52" s="2" t="s">
+      <c r="AE52" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AF52" t="s">
+      <c r="AG52" t="s">
         <v>194</v>
       </c>
-      <c r="AG52">
+      <c r="AH52">
         <v>59.472000000000001</v>
       </c>
-      <c r="AH52">
+      <c r="AI52">
         <v>-137.715</v>
       </c>
-      <c r="AI52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>696705.92950000102</v>
       </c>
       <c r="B53">
         <v>1079552.3197000001</v>
       </c>
-      <c r="C53">
+      <c r="C53" t="s">
+        <v>205</v>
+      </c>
+      <c r="D53">
         <v>52</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>85</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>16</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>1</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>85</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>7.4</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>285</v>
       </c>
-      <c r="M53">
+      <c r="N53">
         <v>112</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>82</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>1.6</v>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <v>98.9</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>1368</v>
       </c>
-      <c r="R53">
+      <c r="S53">
         <v>0.03</v>
       </c>
-      <c r="S53">
+      <c r="T53">
         <v>34</v>
       </c>
-      <c r="T53">
+      <c r="U53">
         <v>122</v>
       </c>
-      <c r="AC53" t="s">
+      <c r="AD53" t="s">
         <v>140</v>
       </c>
-      <c r="AD53" s="2" t="s">
+      <c r="AE53" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF53" t="s">
+      <c r="AG53" t="s">
         <v>192</v>
       </c>
-      <c r="AG53">
+      <c r="AH53">
         <v>64.145930000000007</v>
       </c>
-      <c r="AH53">
+      <c r="AI53">
         <v>-128.45045999999999</v>
       </c>
-      <c r="AI53">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ53">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>706271.39000000095</v>
       </c>
       <c r="B54">
         <v>1082536.5475000001</v>
       </c>
-      <c r="C54">
+      <c r="C54" t="s">
+        <v>205</v>
+      </c>
+      <c r="D54">
         <v>53</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>86</v>
       </c>
-      <c r="AC54" t="s">
+      <c r="AD54" t="s">
         <v>157</v>
       </c>
-      <c r="AD54" t="s">
+      <c r="AE54" t="s">
         <v>177</v>
       </c>
-      <c r="AF54" t="s">
+      <c r="AG54" t="s">
         <v>194</v>
       </c>
-      <c r="AG54">
+      <c r="AH54">
         <v>64.167000000000002</v>
       </c>
-      <c r="AH54">
+      <c r="AI54">
         <v>-128.25</v>
       </c>
-      <c r="AI54">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ54">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>670681.53329999896</v>
       </c>
       <c r="B55">
         <v>1062688.8905</v>
       </c>
-      <c r="C55">
+      <c r="C55" t="s">
+        <v>205</v>
+      </c>
+      <c r="D55">
         <v>54</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>87</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>10</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>15</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>85</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>7.9</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>350</v>
       </c>
-      <c r="M55">
+      <c r="N55">
         <v>102</v>
       </c>
-      <c r="N55">
+      <c r="O55">
         <v>80</v>
       </c>
-      <c r="O55">
+      <c r="P55">
         <v>1.6</v>
       </c>
-      <c r="P55">
+      <c r="Q55">
         <v>106</v>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <v>1182</v>
       </c>
-      <c r="R55">
+      <c r="S55">
         <v>0.03</v>
       </c>
-      <c r="S55">
+      <c r="T55">
         <v>34</v>
       </c>
-      <c r="T55">
+      <c r="U55">
         <v>114</v>
       </c>
-      <c r="AC55" t="s">
+      <c r="AD55" t="s">
         <v>140</v>
       </c>
-      <c r="AD55" s="2" t="s">
+      <c r="AE55" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF55" t="s">
+      <c r="AG55" t="s">
         <v>194</v>
       </c>
-      <c r="AG55">
+      <c r="AH55">
         <v>64.009</v>
       </c>
-      <c r="AH55">
+      <c r="AI55">
         <v>-129.00416999999999</v>
       </c>
-      <c r="AI55">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ55">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>670464.97409999894</v>
       </c>
       <c r="B56">
         <v>1062676.9453</v>
       </c>
-      <c r="C56">
+      <c r="C56" t="s">
+        <v>205</v>
+      </c>
+      <c r="D56">
         <v>55</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>88</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>10</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>1.5</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>85</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>7.87</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>390</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>65</v>
       </c>
-      <c r="N56">
+      <c r="O56">
         <v>420</v>
       </c>
-      <c r="O56">
+      <c r="P56">
         <v>6.2</v>
       </c>
-      <c r="P56">
+      <c r="Q56">
         <v>102</v>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <v>1007</v>
       </c>
-      <c r="R56">
+      <c r="S56">
         <v>0.03</v>
       </c>
-      <c r="S56">
+      <c r="T56">
         <v>34</v>
       </c>
-      <c r="T56">
+      <c r="U56">
         <v>535</v>
       </c>
-      <c r="AC56" t="s">
+      <c r="AD56" t="s">
         <v>140</v>
       </c>
-      <c r="AD56" s="2" t="s">
+      <c r="AE56" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF56" t="s">
+      <c r="AG56" t="s">
         <v>194</v>
       </c>
-      <c r="AG56">
+      <c r="AH56">
         <v>64.009</v>
       </c>
-      <c r="AH56">
+      <c r="AI56">
         <v>-129.00861</v>
       </c>
-      <c r="AI56">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ56">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>698794.77659999998</v>
       </c>
       <c r="B57">
         <v>1072683.6721999999</v>
       </c>
-      <c r="C57">
+      <c r="C57" t="s">
+        <v>205</v>
+      </c>
+      <c r="D57">
         <v>56</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>89</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>46</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>30</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>106</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>7.5</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>260</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>66</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>5850</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <v>80</v>
       </c>
-      <c r="P57">
+      <c r="Q57">
         <v>278</v>
       </c>
-      <c r="Q57">
+      <c r="R57">
         <v>1191</v>
       </c>
-      <c r="S57">
+      <c r="T57">
         <v>54</v>
       </c>
-      <c r="T57">
+      <c r="U57">
         <v>8312</v>
       </c>
-      <c r="AC57" t="s">
+      <c r="AD57" t="s">
         <v>158</v>
       </c>
-      <c r="AD57" s="2" t="s">
+      <c r="AE57" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AF57" t="s">
+      <c r="AG57" t="s">
         <v>194</v>
       </c>
-      <c r="AG57">
+      <c r="AH57">
         <v>64.083330000000004</v>
       </c>
-      <c r="AH57">
+      <c r="AI57">
         <v>-128.41667000000001</v>
       </c>
-      <c r="AI57">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ57">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>403429.4792</v>
       </c>
       <c r="B58">
         <v>609026.33219999995</v>
       </c>
-      <c r="C58">
+      <c r="C58" t="s">
+        <v>205</v>
+      </c>
+      <c r="D58">
         <v>57</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>90</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>17</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>1</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>85</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>8.1999999999999993</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>59</v>
       </c>
-      <c r="M58">
+      <c r="N58">
         <v>13.8</v>
       </c>
-      <c r="N58">
+      <c r="O58">
         <v>1.8</v>
       </c>
-      <c r="O58">
+      <c r="P58">
         <v>0.7</v>
       </c>
-      <c r="P58">
+      <c r="Q58">
         <v>138</v>
       </c>
-      <c r="Q58">
+      <c r="R58">
         <v>5</v>
       </c>
-      <c r="S58">
+      <c r="T58">
         <v>34</v>
       </c>
-      <c r="T58">
+      <c r="U58">
         <v>0.1</v>
       </c>
-      <c r="AC58" t="s">
+      <c r="AD58" t="s">
         <v>142</v>
       </c>
-      <c r="AD58" s="2" t="s">
+      <c r="AE58" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF58" t="s">
+      <c r="AG58" t="s">
         <v>192</v>
       </c>
-      <c r="AG58">
+      <c r="AH58">
         <v>59.969169999999998</v>
       </c>
-      <c r="AH58">
+      <c r="AI58">
         <v>-134.22622999999999</v>
       </c>
-      <c r="AI58">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ58">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>416763.38160000002</v>
       </c>
       <c r="B59">
         <v>598458.77129999897</v>
       </c>
-      <c r="C59">
+      <c r="C59" t="s">
+        <v>205</v>
+      </c>
+      <c r="D59">
         <v>58</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>91</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>13</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>45</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>91</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>7.6</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>58</v>
       </c>
-      <c r="M59">
+      <c r="N59">
         <v>9.8000000000000007</v>
       </c>
-      <c r="N59">
+      <c r="O59">
         <v>2.4</v>
       </c>
-      <c r="O59">
+      <c r="P59">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P59">
+      <c r="Q59">
         <v>114</v>
       </c>
-      <c r="Q59">
+      <c r="R59">
         <v>8.9</v>
       </c>
-      <c r="S59">
+      <c r="T59">
         <v>39</v>
       </c>
-      <c r="T59">
+      <c r="U59">
         <v>0.1</v>
       </c>
-      <c r="AC59" t="s">
+      <c r="AD59" t="s">
         <v>142</v>
       </c>
-      <c r="AD59" s="2" t="s">
+      <c r="AE59" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF59" t="s">
+      <c r="AG59" t="s">
         <v>192</v>
       </c>
-      <c r="AG59">
+      <c r="AH59">
         <v>59.877209999999998</v>
       </c>
-      <c r="AH59">
+      <c r="AI59">
         <v>-133.98356000000001</v>
       </c>
-      <c r="AI59">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>438766.151000001</v>
       </c>
       <c r="B60">
         <v>545393.61289999995</v>
       </c>
-      <c r="C60">
+      <c r="C60" t="s">
+        <v>205</v>
+      </c>
+      <c r="D60">
         <v>59</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>92</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>29</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>15</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>80</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>8.1999999999999993</v>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>67</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>18.5</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>3.4</v>
       </c>
-      <c r="O60">
+      <c r="P60">
         <v>0.7</v>
       </c>
-      <c r="P60">
+      <c r="Q60">
         <v>150</v>
       </c>
-      <c r="Q60">
+      <c r="R60">
         <v>12</v>
       </c>
-      <c r="S60">
+      <c r="T60">
         <v>30</v>
       </c>
-      <c r="T60">
+      <c r="U60">
         <v>0.2</v>
       </c>
-      <c r="AC60" t="s">
+      <c r="AD60" t="s">
         <v>159</v>
       </c>
-      <c r="AD60" s="2" t="s">
+      <c r="AE60" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AF60" t="s">
+      <c r="AG60" t="s">
         <v>197</v>
       </c>
-      <c r="AG60">
+      <c r="AH60">
         <v>59.403939999999999</v>
       </c>
-      <c r="AH60">
+      <c r="AI60">
         <v>-133.57544999999999</v>
       </c>
-      <c r="AI60">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ60">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>492939.82169999898</v>
       </c>
       <c r="B61">
         <v>530250.57069999899</v>
       </c>
-      <c r="C61">
+      <c r="C61" t="s">
+        <v>205</v>
+      </c>
+      <c r="D61">
         <v>60</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>93</v>
       </c>
-      <c r="AC61" t="s">
+      <c r="AD61" t="s">
         <v>160</v>
       </c>
-      <c r="AD61" s="2" t="s">
+      <c r="AE61" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AF61" t="s">
+      <c r="AG61" t="s">
         <v>192</v>
       </c>
-      <c r="AG61">
+      <c r="AH61">
         <v>59.272269999999999</v>
       </c>
-      <c r="AH61">
+      <c r="AI61">
         <v>-132.62351000000001</v>
       </c>
-      <c r="AI61">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ61">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>656367.32509999897</v>
       </c>
       <c r="B62">
         <v>575049.11700000102</v>
       </c>
-      <c r="C62">
+      <c r="C62" t="s">
+        <v>205</v>
+      </c>
+      <c r="D62">
         <v>61</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>94</v>
       </c>
-      <c r="AC62" t="s">
+      <c r="AD62" t="s">
         <v>160</v>
       </c>
-      <c r="AD62" s="2" t="s">
+      <c r="AE62" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AF62" t="s">
+      <c r="AG62" t="s">
         <v>192</v>
       </c>
-      <c r="AG62">
+      <c r="AH62">
         <v>59.64472</v>
       </c>
-      <c r="AH62">
+      <c r="AI62">
         <v>-129.73254</v>
       </c>
-      <c r="AI62">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ62">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>870801.50450000004</v>
       </c>
       <c r="B63">
         <v>575153.17820000101</v>
       </c>
-      <c r="C63">
+      <c r="C63" t="s">
+        <v>205</v>
+      </c>
+      <c r="D63">
         <v>62</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>95</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>42</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>73</v>
       </c>
-      <c r="AC63" t="s">
+      <c r="AD63" t="s">
         <v>161</v>
       </c>
-      <c r="AD63" s="2" t="s">
+      <c r="AE63" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AF63" t="s">
+      <c r="AG63" t="s">
         <v>198</v>
       </c>
-      <c r="AG63">
+      <c r="AH63">
         <v>59.504060000000003</v>
       </c>
-      <c r="AH63">
+      <c r="AI63">
         <v>-125.95632999999999</v>
       </c>
-      <c r="AI63">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ63">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>927946.82979999995</v>
       </c>
       <c r="B64">
         <v>516755.41110000003</v>
       </c>
-      <c r="C64">
+      <c r="C64" t="s">
+        <v>205</v>
+      </c>
+      <c r="D64">
         <v>63</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>96</v>
       </c>
-      <c r="AC64" t="s">
+      <c r="AD64" t="s">
         <v>159</v>
       </c>
-      <c r="AD64" s="2" t="s">
+      <c r="AE64" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AF64" t="s">
+      <c r="AG64" t="s">
         <v>192</v>
       </c>
-      <c r="AG64">
+      <c r="AH64">
         <v>58.92503</v>
       </c>
-      <c r="AH64">
+      <c r="AI64">
         <v>-125.07669</v>
       </c>
-      <c r="AI64">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ64">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>933208.83319999999</v>
       </c>
       <c r="B65">
         <v>581299.26630000002</v>
       </c>
-      <c r="C65">
+      <c r="C65" t="s">
+        <v>205</v>
+      </c>
+      <c r="D65">
         <v>64</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>97</v>
       </c>
-      <c r="AC65" t="s">
+      <c r="AD65" t="s">
         <v>159</v>
       </c>
-      <c r="AD65" s="2" t="s">
+      <c r="AE65" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AE65" t="s">
+      <c r="AF65" t="s">
         <v>188</v>
       </c>
-      <c r="AF65" t="s">
+      <c r="AG65" t="s">
         <v>192</v>
       </c>
-      <c r="AG65">
+      <c r="AH65">
         <v>59.496299999999998</v>
       </c>
-      <c r="AH65">
+      <c r="AI65">
         <v>-124.85186</v>
       </c>
-      <c r="AI65">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ65">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>892352.54859999905</v>
       </c>
       <c r="B66">
         <v>589627.06350000005</v>
       </c>
-      <c r="C66">
+      <c r="C66" t="s">
+        <v>205</v>
+      </c>
+      <c r="D66">
         <v>65</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>98</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>58</v>
       </c>
-      <c r="AC66" t="s">
+      <c r="AD66" t="s">
         <v>157</v>
       </c>
-      <c r="AD66" t="s">
+      <c r="AE66" t="s">
         <v>177</v>
       </c>
-      <c r="AF66" t="s">
+      <c r="AG66" t="s">
         <v>192</v>
       </c>
-      <c r="AG66">
+      <c r="AH66">
         <v>59.612949999999998</v>
       </c>
-      <c r="AH66">
+      <c r="AI66">
         <v>-125.55107</v>
       </c>
-      <c r="AI66">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ66">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>786428.422599999</v>
       </c>
       <c r="B67">
         <v>846634.54529999895</v>
       </c>
-      <c r="C67">
+      <c r="C67" t="s">
+        <v>205</v>
+      </c>
+      <c r="D67">
         <v>66</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>99</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>3</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>25</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>101</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>6.4</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>58</v>
       </c>
-      <c r="M67">
+      <c r="N67">
         <v>11</v>
       </c>
-      <c r="N67">
+      <c r="O67">
         <v>1.2</v>
       </c>
-      <c r="O67">
+      <c r="P67">
         <v>0.8</v>
       </c>
-      <c r="P67">
+      <c r="Q67">
         <v>30.4</v>
       </c>
-      <c r="Q67">
+      <c r="R67">
         <v>169</v>
       </c>
-      <c r="S67">
+      <c r="T67">
         <v>48</v>
       </c>
-      <c r="AC67" t="s">
+      <c r="AD67" t="s">
         <v>140</v>
       </c>
-      <c r="AD67" s="2" t="s">
+      <c r="AE67" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF67" t="s">
+      <c r="AG67" t="s">
         <v>194</v>
       </c>
-      <c r="AG67">
+      <c r="AH67">
         <v>62.00365</v>
       </c>
-      <c r="AH67">
+      <c r="AI67">
         <v>-127.02467</v>
       </c>
-      <c r="AI67">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ67">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>697600.88729999994</v>
       </c>
       <c r="B68">
         <v>1079617.5212000001</v>
       </c>
-      <c r="C68">
+      <c r="C68" t="s">
+        <v>205</v>
+      </c>
+      <c r="D68">
         <v>67</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>100</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>22</v>
       </c>
-      <c r="F68">
-        <v>7</v>
-      </c>
       <c r="G68">
+        <v>7</v>
+      </c>
+      <c r="H68">
         <v>90</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>7.3</v>
       </c>
-      <c r="L68">
+      <c r="M68">
         <v>155</v>
       </c>
-      <c r="M68">
+      <c r="N68">
         <v>60</v>
       </c>
-      <c r="N68">
+      <c r="O68">
         <v>2.8</v>
       </c>
-      <c r="O68">
+      <c r="P68">
         <v>0.7</v>
       </c>
-      <c r="P68">
+      <c r="Q68">
         <v>78.7</v>
       </c>
-      <c r="Q68">
+      <c r="R68">
         <v>827</v>
       </c>
-      <c r="R68">
+      <c r="S68">
         <v>0.03</v>
       </c>
-      <c r="S68">
+      <c r="T68">
         <v>38</v>
       </c>
-      <c r="T68">
+      <c r="U68">
         <v>1.8</v>
       </c>
-      <c r="AC68" t="s">
+      <c r="AD68" t="s">
         <v>140</v>
       </c>
-      <c r="AD68" s="2" t="s">
+      <c r="AE68" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF68" t="s">
+      <c r="AG68" t="s">
         <v>192</v>
       </c>
-      <c r="AG68">
+      <c r="AH68">
         <v>64.146000000000001</v>
       </c>
-      <c r="AH68">
+      <c r="AI68">
         <v>-128.43199999999999</v>
       </c>
-      <c r="AI68">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ68">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>-132782.94409999999</v>
       </c>
       <c r="B69">
         <v>1239975.9634</v>
       </c>
-      <c r="C69">
+      <c r="C69" t="s">
+        <v>205</v>
+      </c>
+      <c r="D69">
         <v>68</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>101</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>74</v>
       </c>
-      <c r="AC69" t="s">
+      <c r="AD69" t="s">
         <v>162</v>
       </c>
-      <c r="AD69" s="2" t="s">
+      <c r="AE69" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="AF69" t="s">
+      <c r="AG69" t="s">
         <v>194</v>
       </c>
-      <c r="AG69">
+      <c r="AH69">
         <v>65.030983399999997</v>
       </c>
-      <c r="AH69">
+      <c r="AI69">
         <v>-146.05243350000001</v>
       </c>
-      <c r="AI69">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>-66812.324699999794</v>
       </c>
       <c r="B70">
         <v>1243914.1894</v>
       </c>
-      <c r="C70">
+      <c r="C70" t="s">
+        <v>205</v>
+      </c>
+      <c r="D70">
         <v>69</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>102</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>61</v>
       </c>
-      <c r="AC70" t="s">
+      <c r="AD70" t="s">
         <v>163</v>
       </c>
-      <c r="AD70" s="2" t="s">
+      <c r="AE70" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="AF70" t="s">
+      <c r="AG70" t="s">
         <v>199</v>
       </c>
-      <c r="AG70">
+      <c r="AH70">
         <v>65.184661000000006</v>
       </c>
-      <c r="AH70">
+      <c r="AI70">
         <v>-144.692004</v>
       </c>
-      <c r="AI70">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ70">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>-57144.195299999803</v>
       </c>
       <c r="B71">
         <v>1276707.7449</v>
       </c>
-      <c r="C71">
+      <c r="C71" t="s">
+        <v>205</v>
+      </c>
+      <c r="D71">
         <v>70</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>103</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>57.2</v>
       </c>
-      <c r="AC71" t="s">
+      <c r="AD71" t="s">
         <v>164</v>
       </c>
-      <c r="AD71" s="2" t="s">
+      <c r="AE71" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AE71" t="s">
+      <c r="AF71" t="s">
         <v>189</v>
       </c>
-      <c r="AF71" t="s">
+      <c r="AG71" t="s">
         <v>194</v>
       </c>
-      <c r="AG71">
+      <c r="AH71">
         <v>65.489453999999995</v>
       </c>
-      <c r="AH71">
+      <c r="AI71">
         <v>-144.62231399999999</v>
       </c>
-      <c r="AI71">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ71">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>21929.395999999699</v>
       </c>
       <c r="B72">
         <v>1218689.8705</v>
       </c>
-      <c r="C72">
+      <c r="C72" t="s">
+        <v>205</v>
+      </c>
+      <c r="D72">
         <v>71</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>104</v>
       </c>
-      <c r="AC72" t="s">
+      <c r="AD72" t="s">
         <v>165</v>
       </c>
-      <c r="AD72" s="2" t="s">
+      <c r="AE72" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AE72" t="s">
+      <c r="AF72" t="s">
         <v>190</v>
       </c>
-      <c r="AF72" t="s">
+      <c r="AG72" t="s">
         <v>200</v>
       </c>
-      <c r="AG72">
+      <c r="AH72">
         <v>65.102091999999999</v>
       </c>
-      <c r="AH72">
+      <c r="AI72">
         <v>-142.73262700000001</v>
       </c>
-      <c r="AI72">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ72">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>-5595.2453000005298</v>
       </c>
       <c r="B73">
         <v>1153857.4432000001</v>
       </c>
-      <c r="C73">
+      <c r="C73" t="s">
+        <v>205</v>
+      </c>
+      <c r="D73">
         <v>72</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>105</v>
       </c>
-      <c r="AC73" t="s">
+      <c r="AD73" t="s">
         <v>165</v>
       </c>
-      <c r="AD73" s="2" t="s">
+      <c r="AE73" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AE73" t="s">
+      <c r="AF73" t="s">
         <v>191</v>
       </c>
-      <c r="AF73" t="s">
+      <c r="AG73" t="s">
         <v>201</v>
       </c>
-      <c r="AG73">
+      <c r="AH73">
         <v>64.488980999999995</v>
       </c>
-      <c r="AH73">
+      <c r="AI73">
         <v>-143.081535</v>
       </c>
-      <c r="AI73">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ73">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>-29817.8704000004</v>
       </c>
       <c r="B74">
         <v>751074.2071</v>
       </c>
-      <c r="C74">
+      <c r="C74" t="s">
+        <v>205</v>
+      </c>
+      <c r="D74">
         <v>73</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>106</v>
       </c>
-      <c r="AC74" t="s">
+      <c r="AD74" t="s">
         <v>165</v>
       </c>
-      <c r="AD74" s="2" t="s">
+      <c r="AE74" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF74" t="s">
+      <c r="AG74" t="s">
         <v>202</v>
       </c>
-      <c r="AG74">
+      <c r="AH74">
         <v>60.889150999999998</v>
       </c>
-      <c r="AH74">
+      <c r="AI74">
         <v>-142.28966800000001</v>
       </c>
-      <c r="AI74">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ74">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>209789.15779999999</v>
       </c>
       <c r="B75">
         <v>474269.1874</v>
       </c>
-      <c r="C75">
+      <c r="C75" t="s">
+        <v>205</v>
+      </c>
+      <c r="D75">
         <v>74</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>107</v>
       </c>
-      <c r="AC75" t="s">
+      <c r="AD75" t="s">
         <v>165</v>
       </c>
-      <c r="AD75" s="2" t="s">
+      <c r="AE75" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF75" t="s">
+      <c r="AG75" t="s">
         <v>202</v>
       </c>
-      <c r="AG75">
+      <c r="AH75">
         <v>58.665373000000002</v>
       </c>
-      <c r="AH75">
+      <c r="AI75">
         <v>-137.48856599999999</v>
       </c>
-      <c r="AI75">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ75">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>299332.26120000001</v>
       </c>
       <c r="B76">
         <v>407958.78409999999</v>
       </c>
-      <c r="C76">
+      <c r="C76" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76">
         <v>75</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>108</v>
       </c>
-      <c r="E76">
+      <c r="F76">
         <v>46</v>
       </c>
-      <c r="AC76" t="s">
+      <c r="AD76" t="s">
         <v>166</v>
       </c>
-      <c r="AD76" s="2" t="s">
+      <c r="AE76" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AF76" t="s">
+      <c r="AG76" t="s">
         <v>195</v>
       </c>
-      <c r="AG76">
+      <c r="AH76">
         <v>58.122278999999999</v>
       </c>
-      <c r="AH76">
+      <c r="AI76">
         <v>-135.89210299999999</v>
       </c>
-      <c r="AI76">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ76">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>296574.62989999901</v>
       </c>
       <c r="B77">
         <v>395148.03739999997</v>
       </c>
-      <c r="C77">
+      <c r="C77" t="s">
+        <v>205</v>
+      </c>
+      <c r="D77">
         <v>76</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>109</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>76</v>
       </c>
-      <c r="AC77" t="s">
+      <c r="AD77" t="s">
         <v>165</v>
       </c>
-      <c r="AD77" s="2" t="s">
+      <c r="AE77" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AF77" t="s">
+      <c r="AG77" t="s">
         <v>195</v>
       </c>
-      <c r="AG77">
+      <c r="AH77">
         <v>58.005581999999997</v>
       </c>
-      <c r="AH77">
+      <c r="AI77">
         <v>-135.92693399999999</v>
       </c>
-      <c r="AI77">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ77">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>289118.69420000003</v>
       </c>
       <c r="B78">
         <v>377172.43119999999</v>
       </c>
-      <c r="C78">
+      <c r="C78" t="s">
+        <v>205</v>
+      </c>
+      <c r="D78">
         <v>77</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>110</v>
       </c>
-      <c r="AC78" t="s">
+      <c r="AD78" t="s">
         <v>165</v>
       </c>
-      <c r="AD78" s="2" t="s">
+      <c r="AE78" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF78" t="s">
+      <c r="AG78" t="s">
         <v>195</v>
       </c>
-      <c r="AG78">
+      <c r="AH78">
         <v>57.839992000000002</v>
       </c>
-      <c r="AH78">
+      <c r="AI78">
         <v>-136.03541200000001</v>
       </c>
-      <c r="AI78">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ78">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>299996.787799999</v>
       </c>
       <c r="B79">
         <v>368797.54840000003</v>
       </c>
-      <c r="C79">
+      <c r="C79" t="s">
+        <v>205</v>
+      </c>
+      <c r="D79">
         <v>78</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>111</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>39</v>
       </c>
-      <c r="AC79" t="s">
+      <c r="AD79" t="s">
         <v>165</v>
       </c>
-      <c r="AD79" s="2" t="s">
+      <c r="AE79" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF79" t="s">
+      <c r="AG79" t="s">
         <v>195</v>
       </c>
-      <c r="AG79">
+      <c r="AH79">
         <v>57.769868000000002</v>
       </c>
-      <c r="AH79">
+      <c r="AI79">
         <v>-135.84598800000001</v>
       </c>
-      <c r="AI79">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ79">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>270810.7622</v>
       </c>
       <c r="B80">
         <v>374472.51799999899</v>
       </c>
-      <c r="C80">
+      <c r="C80" t="s">
+        <v>205</v>
+      </c>
+      <c r="D80">
         <v>79</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>112</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>57.2</v>
       </c>
-      <c r="AC80" t="s">
+      <c r="AD80" t="s">
         <v>165</v>
       </c>
-      <c r="AD80" s="2" t="s">
+      <c r="AE80" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF80" t="s">
+      <c r="AG80" t="s">
         <v>194</v>
       </c>
-      <c r="AG80">
+      <c r="AH80">
         <v>57.806075</v>
       </c>
-      <c r="AH80">
+      <c r="AI80">
         <v>-136.33888400000001</v>
       </c>
-      <c r="AI80">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ80">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>337451.16259999899</v>
       </c>
       <c r="B81">
         <v>367917.41840000101</v>
       </c>
-      <c r="C81">
+      <c r="C81" t="s">
+        <v>205</v>
+      </c>
+      <c r="D81">
         <v>80</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>113</v>
       </c>
-      <c r="E81">
+      <c r="F81">
         <v>41.1</v>
       </c>
-      <c r="AC81" t="s">
+      <c r="AD81" t="s">
         <v>165</v>
       </c>
-      <c r="AD81" s="2" t="s">
+      <c r="AE81" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF81" t="s">
+      <c r="AG81" t="s">
         <v>194</v>
       </c>
-      <c r="AG81">
+      <c r="AH81">
         <v>57.778095</v>
       </c>
-      <c r="AH81">
+      <c r="AI81">
         <v>-135.219618</v>
       </c>
-      <c r="AI81">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ81">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>323201.11150000099</v>
       </c>
       <c r="B82">
         <v>265284.2194</v>
       </c>
-      <c r="C82">
+      <c r="C82" t="s">
+        <v>205</v>
+      </c>
+      <c r="D82">
         <v>81</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>114</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>67.2</v>
       </c>
-      <c r="AC82" t="s">
+      <c r="AD82" t="s">
         <v>165</v>
       </c>
-      <c r="AD82" s="2" t="s">
+      <c r="AE82" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF82" t="s">
+      <c r="AG82" t="s">
         <v>194</v>
       </c>
-      <c r="AG82">
+      <c r="AH82">
         <v>56.846530999999999</v>
       </c>
-      <c r="AH82">
+      <c r="AI82">
         <v>-135.379772</v>
       </c>
-      <c r="AI82">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ82">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>363517.24690000003</v>
       </c>
       <c r="B83">
         <v>249498.2849</v>
       </c>
-      <c r="C83">
+      <c r="C83" t="s">
+        <v>205</v>
+      </c>
+      <c r="D83">
         <v>82</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>115</v>
       </c>
-      <c r="AC83" t="s">
+      <c r="AD83" t="s">
         <v>165</v>
       </c>
-      <c r="AD83" s="2" t="s">
+      <c r="AE83" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF83" t="s">
+      <c r="AG83" t="s">
         <v>195</v>
       </c>
-      <c r="AG83">
+      <c r="AH83">
         <v>56.718592000000001</v>
       </c>
-      <c r="AH83">
+      <c r="AI83">
         <v>-134.71472800000001</v>
       </c>
-      <c r="AI83">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ83">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>357889.4241</v>
       </c>
       <c r="B84">
         <v>290789.11859999999</v>
       </c>
-      <c r="C84">
+      <c r="C84" t="s">
+        <v>205</v>
+      </c>
+      <c r="D84">
         <v>83</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>116</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>51.1</v>
       </c>
-      <c r="AC84" t="s">
+      <c r="AD84" t="s">
         <v>165</v>
       </c>
-      <c r="AD84" s="2" t="s">
+      <c r="AE84" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF84" t="s">
+      <c r="AG84" t="s">
         <v>194</v>
       </c>
-      <c r="AG84">
+      <c r="AH84">
         <v>57.089672299999997</v>
       </c>
-      <c r="AH84">
+      <c r="AI84">
         <v>-134.83058969999999</v>
       </c>
-      <c r="AI84">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ84">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>527589.30959999899</v>
       </c>
       <c r="B85">
         <v>248123.57929999899</v>
       </c>
-      <c r="C85">
+      <c r="C85" t="s">
+        <v>205</v>
+      </c>
+      <c r="D85">
         <v>84</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>117</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>60</v>
       </c>
-      <c r="AC85" t="s">
+      <c r="AD85" t="s">
         <v>165</v>
       </c>
-      <c r="AD85" s="2" t="s">
+      <c r="AE85" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AF85" t="s">
+      <c r="AG85" t="s">
         <v>194</v>
       </c>
-      <c r="AG85">
+      <c r="AH85">
         <v>56.726835999999999</v>
       </c>
-      <c r="AH85">
+      <c r="AI85">
         <v>-132.05231000000001</v>
       </c>
-      <c r="AI85">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ85">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>515224.80910000001</v>
       </c>
       <c r="B86">
         <v>239633.999199999</v>
       </c>
-      <c r="C86">
+      <c r="C86" t="s">
+        <v>205</v>
+      </c>
+      <c r="D86">
         <v>85</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>118</v>
       </c>
-      <c r="AC86" t="s">
+      <c r="AD86" t="s">
         <v>154</v>
       </c>
-      <c r="AD86" s="2" t="s">
+      <c r="AE86" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AF86" t="s">
+      <c r="AG86" t="s">
         <v>202</v>
       </c>
-      <c r="AG86">
+      <c r="AH86">
         <v>56.650697600000001</v>
       </c>
-      <c r="AH86">
+      <c r="AI86">
         <v>-132.2534895</v>
       </c>
-      <c r="AI86">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ86">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>518633.29880000098</v>
       </c>
       <c r="B87">
         <v>246078.479599999</v>
       </c>
-      <c r="C87">
+      <c r="C87" t="s">
+        <v>205</v>
+      </c>
+      <c r="D87">
         <v>86</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>119</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>21</v>
       </c>
-      <c r="F87">
+      <c r="G87">
         <v>4.5</v>
       </c>
-      <c r="AC87" t="s">
+      <c r="AD87" t="s">
         <v>153</v>
       </c>
-      <c r="AD87" s="2" t="s">
+      <c r="AE87" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AF87" t="s">
+      <c r="AG87" t="s">
         <v>202</v>
       </c>
-      <c r="AG87">
+      <c r="AH87">
         <v>56.708827100000001</v>
       </c>
-      <c r="AH87">
+      <c r="AI87">
         <v>-132.19780040000001</v>
       </c>
-      <c r="AI87">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ87">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>493647.848999999</v>
       </c>
       <c r="B88">
         <v>218200.45570000101</v>
       </c>
-      <c r="C88">
+      <c r="C88" t="s">
+        <v>205</v>
+      </c>
+      <c r="D88">
         <v>87</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>120</v>
       </c>
-      <c r="AC88" t="s">
+      <c r="AD88" t="s">
         <v>154</v>
       </c>
-      <c r="AD88" s="2" t="s">
+      <c r="AE88" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AF88" t="s">
+      <c r="AG88" t="s">
         <v>202</v>
       </c>
-      <c r="AG88">
+      <c r="AH88">
         <v>56.457094499999997</v>
       </c>
-      <c r="AH88">
+      <c r="AI88">
         <v>-132.6023179</v>
       </c>
-      <c r="AI88">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ88">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>595398.46620000002</v>
       </c>
       <c r="B89">
         <v>185203.157600001</v>
       </c>
-      <c r="C89">
+      <c r="C89" t="s">
+        <v>205</v>
+      </c>
+      <c r="D89">
         <v>88</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>121</v>
       </c>
-      <c r="AC89" t="s">
+      <c r="AD89" t="s">
         <v>154</v>
       </c>
-      <c r="AD89" s="2" t="s">
+      <c r="AE89" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AF89" t="s">
+      <c r="AG89" t="s">
         <v>195</v>
       </c>
-      <c r="AG89">
+      <c r="AH89">
         <v>56.148227599999998</v>
       </c>
-      <c r="AH89">
+      <c r="AI89">
         <v>-130.97673130000001</v>
       </c>
-      <c r="AI89">
+      <c r="AJ89">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AD2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="AD3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="AD4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="AD9" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="AD10" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="AD11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="AD12" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="AD13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="AD14" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="AD15" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="AD16" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="AD17" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="AD18" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="AD19" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="AD21" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="AD22" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="AD27" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="AD36" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="AD37" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="AD38" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="AD39" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="AD40" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="AD42" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="AD43" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="AD44" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="AD45" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="AD46" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="AD47" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="AD48" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="AD49" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="AD50" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="AD51" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="AD52" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="AD53" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="AD55" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="AD56" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="AD57" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="AD58" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="AD59" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="AD60" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="AD61" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="AD62" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="AD63" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="AD64" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="AD65" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="AD67" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="AD68" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="AD69" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="AD70" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="AD71" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="AD72" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="AD73" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="AD74" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="AD75" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="AD76" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="AD77" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="AD78" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="AD79" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="AD80" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="AD81" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="AD82" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="AD83" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="AD84" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="AD85" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="AD86" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="AD87" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="AD88" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="AD89" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="AE2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="AE3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="AE4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="AE9" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="AE10" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="AE11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="AE12" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="AE13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="AE14" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="AE15" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="AE16" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="AE17" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="AE18" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="AE19" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="AE21" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="AE22" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="AE27" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="AE36" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="AE37" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="AE38" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="AE39" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="AE40" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="AE42" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="AE43" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="AE44" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="AE45" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="AE46" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="AE47" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="AE48" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="AE49" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="AE50" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="AE51" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="AE52" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="AE53" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="AE55" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="AE56" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="AE57" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="AE58" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="AE59" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="AE60" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="AE61" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="AE62" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="AE63" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="AE64" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="AE65" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="AE67" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="AE68" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="AE69" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="AE70" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="AE71" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="AE72" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="AE73" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="AE74" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="AE75" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="AE76" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="AE77" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="AE78" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="AE79" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="AE80" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="AE81" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="AE82" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="AE83" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="AE84" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="AE85" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="AE86" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="AE87" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="AE88" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="AE89" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
